--- a/Data/20_scenarios.xlsx
+++ b/Data/20_scenarios.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Control" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Scenarios" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Notes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Motor_Scenarios" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -987,4 +988,500 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="95" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Driver F -- auxiliary motor content scenarios. Added 2026-08-12.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>WHY SCENARIOS AND NOT A WIDER BAND. A triangular Min/Mode/Max says 'the truth is somewhere</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>in this range, most likely near the mode'. That is right for MEASUREMENT uncertainty. But</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>whether Chinese-style executive interiors become the European norm is a STRUCTURAL FORK:</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>either they do or they do not, and those are two different worlds, not two points on a</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>continuum. A single band with mode 1.35 for EF describes a world nobody expects -- the</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>average of 'Europe stays European' (~1.15) and 'Europe adopts Chinese content' (~1.50).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>This is the same argument the project already makes for architecture states:</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  'A vehicle is one design, never a blend. Share-weighting collapses a bimodal mixture</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   into its mean and destroys the band.'  (PCB_MODEL_DESIGN.md 2.2d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>MECHANISM. One scenario drawn per vehicle by Weight and HELD ACROSS ALL YEARS, then the</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>headroom drawn inside that scenario. Output is bimodal, which is the truth, rather than a</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>smeared unimodal band. Set Control!B4 to a scenario Name to pin one, or SAMPLE to draw.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>THE GRADIENT AB &gt; CD &gt; EF HOLDS INSIDE EVERY SCENARIO -- validation M4 tests the mechanism,</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>so it must not be satisfied only on average.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>EVIDENCE: docs/AUX_MOTOR_ADOPTION_RESEARCH.md sections 7 and 8. The EF numbers rest on an</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>adjustment-AXIS build-up (one motor per 'way'), not on a fitment survey -- ASSUMPTION.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Segment</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Headroom_Min</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Headroom_Mode</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>Headroom_Max</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>Mechanism</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MS1</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>European_Content</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>EF feature set is complete; AB/CD keep closing the European gap. Liftgate 20-&gt;40%+ by 2030, e-latch 10.7% CAGR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MS1</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>European_Content</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MS1</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>European_Content</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EF</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>EF near-saturated on European content: power seats/windows universal, &gt;62% hands-free liftgate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MS2</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Chinese_Convergence</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Chinese executive-interior adjustment axes become the European premium norm and cascade down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>MS2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Chinese_Convergence</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MS2</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Chinese_Convergence</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EF</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2 front x 14-way + 2 rear x 10-way = 48 seat motors vs ~18.5 implied by 05_. Rear legrest/footrest/thigh/lumbar. Same China-leads-Europe-follows mechanism as lidar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MS3</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Cost_Constrained</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Content growth checked by affordability; smart motors carry a 25-40% price premium.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>MS3</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Cost_Constrained</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CD</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>MS3</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Cost_Constrained</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EF</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Integration (one multi-function actuator replacing two) offsets feature growth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Weights sum (must be 1.000)</t>
+        </is>
+      </c>
+      <c r="G35">
+        <f>SUM(G25,G28,G31)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>